--- a/şns_topu.xlsx
+++ b/şns_topu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\slck\Kaptan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2C1EDD-AC29-428A-9336-209E3CC4F7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A72ABDC-6538-4E0C-A059-68259A0AE74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -483,166 +483,166 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="8">
-        <v>46222</v>
+        <v>46225</v>
       </c>
       <c r="C3" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3" s="7">
         <v>15</v>
       </c>
       <c r="E3" s="7">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G3" s="7">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
+        <v>57</v>
+      </c>
+      <c r="B4" s="6">
+        <v>46222</v>
+      </c>
+      <c r="C4" s="5">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5">
+        <v>31</v>
+      </c>
+      <c r="G4" s="5">
+        <v>34</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>56</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B5" s="6">
         <v>46218</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D5" s="5">
         <v>3</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E5" s="5">
         <v>6</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F5" s="5">
         <v>14</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G5" s="5">
         <v>15</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H5" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <v>55</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B6" s="6">
         <v>46215</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C6" s="5">
         <v>10</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D6" s="5">
         <v>19</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E6" s="5">
         <v>22</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F6" s="5">
         <v>25</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G6" s="5">
         <v>26</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H6" s="5">
         <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>54</v>
-      </c>
-      <c r="B6" s="3">
-        <v>46211</v>
-      </c>
-      <c r="C6" s="2">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2">
-        <v>15</v>
-      </c>
-      <c r="F6" s="2">
-        <v>19</v>
-      </c>
-      <c r="G6" s="2">
-        <v>22</v>
-      </c>
-      <c r="H6" s="2">
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3">
-        <v>46208</v>
+        <v>46211</v>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F7" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2">
         <v>7</v>
       </c>
       <c r="E8" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H8" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="3">
-        <v>46201</v>
+        <v>46204</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -651,221 +651,221 @@
         <v>7</v>
       </c>
       <c r="E9" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F9" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3">
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
         <v>7</v>
       </c>
-      <c r="D10" s="2">
-        <v>26</v>
-      </c>
       <c r="E10" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G10" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H10" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3">
-        <v>46194</v>
+        <v>46197</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G11" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="3">
-        <v>46190</v>
+        <v>46194</v>
       </c>
       <c r="C12" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E12" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2">
         <v>22</v>
       </c>
       <c r="G12" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="3">
-        <v>46187</v>
+        <v>46190</v>
       </c>
       <c r="C13" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2">
         <v>22</v>
       </c>
       <c r="G13" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H13" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3">
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2">
+        <v>21</v>
+      </c>
+      <c r="F14" s="2">
+        <v>22</v>
+      </c>
+      <c r="G14" s="2">
+        <v>32</v>
+      </c>
+      <c r="H14" s="2">
         <v>2</v>
-      </c>
-      <c r="D14" s="2">
-        <v>4</v>
-      </c>
-      <c r="E14" s="2">
-        <v>13</v>
-      </c>
-      <c r="F14" s="2">
-        <v>24</v>
-      </c>
-      <c r="G14" s="2">
-        <v>33</v>
-      </c>
-      <c r="H14" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="3">
-        <v>46180</v>
+        <v>46183</v>
       </c>
       <c r="C15" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F15" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G15" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="3">
-        <v>46176</v>
+        <v>46180</v>
       </c>
       <c r="C16" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" s="2">
         <v>21</v>
       </c>
       <c r="G16" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H16" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="3">
-        <v>46173</v>
+        <v>46176</v>
       </c>
       <c r="C17" s="2">
         <v>7</v>
       </c>
       <c r="D17" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E17" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F17" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2">
         <v>14</v>
@@ -873,94 +873,94 @@
     </row>
     <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="3">
-        <v>46169</v>
+        <v>46173</v>
       </c>
       <c r="C18" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D18" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F18" s="2">
         <v>22</v>
       </c>
       <c r="G18" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="3">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="C19" s="2">
         <v>18</v>
       </c>
       <c r="D19" s="2">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2">
         <v>20</v>
       </c>
-      <c r="E19" s="2">
-        <v>26</v>
-      </c>
       <c r="F19" s="2">
+        <v>22</v>
+      </c>
+      <c r="G19" s="2">
         <v>27</v>
       </c>
-      <c r="G19" s="2">
-        <v>34</v>
-      </c>
       <c r="H19" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="C20" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2">
+        <v>26</v>
+      </c>
+      <c r="F20" s="2">
         <v>27</v>
-      </c>
-      <c r="F20" s="2">
-        <v>31</v>
       </c>
       <c r="G20" s="2">
         <v>34</v>
       </c>
       <c r="H20" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="3">
-        <v>46159</v>
+        <v>46162</v>
       </c>
       <c r="C21" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D21" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2">
         <v>27</v>
@@ -969,111 +969,111 @@
         <v>31</v>
       </c>
       <c r="G21" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H21" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="3">
-        <v>46155</v>
+        <v>46159</v>
       </c>
       <c r="C22" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F22" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="G22" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H22" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3">
-        <v>46152</v>
+        <v>46155</v>
       </c>
       <c r="C23" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="2">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" s="2">
+        <v>21</v>
+      </c>
+      <c r="H23" s="2">
         <v>6</v>
-      </c>
-      <c r="E23" s="2">
-        <v>20</v>
-      </c>
-      <c r="F23" s="2">
-        <v>23</v>
-      </c>
-      <c r="G23" s="2">
-        <v>33</v>
-      </c>
-      <c r="H23" s="2">
-        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="3">
-        <v>46148</v>
+        <v>46152</v>
       </c>
       <c r="C24" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2">
         <v>20</v>
       </c>
-      <c r="E24" s="2">
-        <v>25</v>
-      </c>
       <c r="F24" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G24" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="C25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F25" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G25" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H25" s="2">
         <v>13</v>
@@ -1081,129 +1081,129 @@
     </row>
     <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="3">
-        <v>46141</v>
+        <v>46145</v>
       </c>
       <c r="C26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F26" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H26" s="2">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="3">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
         <v>6</v>
       </c>
-      <c r="D27" s="2">
-        <v>17</v>
-      </c>
       <c r="E27" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F27" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G27" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H27" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
+        <v>33</v>
+      </c>
+      <c r="B28" s="3">
+        <v>46138</v>
+      </c>
+      <c r="C28" s="2">
+        <v>6</v>
+      </c>
+      <c r="D28" s="2">
+        <v>17</v>
+      </c>
+      <c r="E28" s="2">
+        <v>26</v>
+      </c>
+      <c r="F28" s="2">
+        <v>29</v>
+      </c>
+      <c r="G28" s="2">
         <v>32</v>
       </c>
-      <c r="B28" s="3">
-        <v>46134</v>
-      </c>
-      <c r="C28" s="2">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2">
-        <v>16</v>
-      </c>
-      <c r="E28" s="2">
-        <v>24</v>
-      </c>
-      <c r="F28" s="2">
-        <v>31</v>
-      </c>
-      <c r="G28" s="2">
-        <v>34</v>
-      </c>
       <c r="H28" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3">
+        <v>46134</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>16</v>
+      </c>
+      <c r="E29" s="2">
+        <v>24</v>
+      </c>
+      <c r="F29" s="2">
         <v>31</v>
-      </c>
-      <c r="B29" s="3">
-        <v>46131</v>
-      </c>
-      <c r="C29" s="2">
-        <v>3</v>
-      </c>
-      <c r="D29" s="2">
-        <v>14</v>
-      </c>
-      <c r="E29" s="2">
-        <v>16</v>
-      </c>
-      <c r="F29" s="2">
-        <v>17</v>
       </c>
       <c r="G29" s="2">
         <v>34</v>
       </c>
       <c r="H29" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="3">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="C30" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" s="2">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H30" s="2">
         <v>13</v>
@@ -1211,259 +1211,259 @@
     </row>
     <row r="31" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
         <v>2</v>
       </c>
-      <c r="D31" s="2">
-        <v>6</v>
-      </c>
       <c r="E31" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F31" s="2">
+        <v>16</v>
+      </c>
+      <c r="G31" s="2">
         <v>19</v>
       </c>
-      <c r="G31" s="2">
-        <v>24</v>
-      </c>
       <c r="H31" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="3">
-        <v>46120</v>
+        <v>46124</v>
       </c>
       <c r="C32" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E32" s="2">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G32" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H32" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33" s="3">
-        <v>46117</v>
+        <v>46120</v>
       </c>
       <c r="C33" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E33" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F33" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G33" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B34" s="3">
-        <v>46113</v>
+        <v>46117</v>
       </c>
       <c r="C34" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E34" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F34" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G34" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H34" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B35" s="3">
-        <v>46110</v>
+        <v>46113</v>
       </c>
       <c r="C35" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D35" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E35" s="2">
         <v>12</v>
       </c>
       <c r="F35" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G35" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H35" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36" s="3">
-        <v>46106</v>
+        <v>46110</v>
       </c>
       <c r="C36" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D36" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F36" s="2">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G36" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B37" s="3">
-        <v>46103</v>
+        <v>46106</v>
       </c>
       <c r="C37" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F37" s="2">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G37" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H37" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B38" s="3">
-        <v>46099</v>
+        <v>46103</v>
       </c>
       <c r="C38" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E38" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F38" s="2">
+        <v>18</v>
+      </c>
+      <c r="G38" s="2">
         <v>29</v>
       </c>
-      <c r="G38" s="2">
-        <v>31</v>
-      </c>
       <c r="H38" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B39" s="3">
-        <v>46096</v>
+        <v>46099</v>
       </c>
       <c r="C39" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E39" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F39" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G39" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H39" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
+        <v>21</v>
+      </c>
+      <c r="B40" s="3">
+        <v>46096</v>
+      </c>
+      <c r="C40" s="2">
+        <v>7</v>
+      </c>
+      <c r="D40" s="2">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2">
+        <v>10</v>
+      </c>
+      <c r="F40" s="2">
         <v>20</v>
       </c>
-      <c r="B40" s="3">
-        <v>46092</v>
-      </c>
-      <c r="C40" s="2">
-        <v>6</v>
-      </c>
-      <c r="D40" s="2">
-        <v>11</v>
-      </c>
-      <c r="E40" s="2">
-        <v>14</v>
-      </c>
-      <c r="F40" s="2">
-        <v>24</v>
-      </c>
       <c r="G40" s="2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H40" s="2">
         <v>14</v>
@@ -1471,181 +1471,181 @@
     </row>
     <row r="41" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41" s="3">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D41" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E41" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F41" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G41" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H41" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B42" s="3">
-        <v>46085</v>
+        <v>46089</v>
       </c>
       <c r="C42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F42" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G42" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H42" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B43" s="3">
-        <v>46082</v>
+        <v>46085</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E43" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F43" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G43" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H43" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B44" s="3">
-        <v>46078</v>
+        <v>46082</v>
       </c>
       <c r="C44" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E44" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F44" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G44" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H44" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
+        <v>16</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46078</v>
+      </c>
+      <c r="C45" s="2">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2">
         <v>15</v>
-      </c>
-      <c r="B45" s="3">
-        <v>46075</v>
-      </c>
-      <c r="C45" s="2">
-        <v>3</v>
-      </c>
-      <c r="D45" s="2">
-        <v>11</v>
       </c>
       <c r="E45" s="2">
         <v>24</v>
       </c>
       <c r="F45" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G45" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H45" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B46" s="3">
-        <v>46071</v>
+        <v>46075</v>
       </c>
       <c r="C46" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D46" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E46" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F46" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G46" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H46" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B47" s="3">
-        <v>46068</v>
+        <v>46071</v>
       </c>
       <c r="C47" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D47" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E47" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G47" s="2">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H47" s="2">
         <v>12</v>
@@ -1653,13 +1653,13 @@
     </row>
     <row r="48" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48" s="3">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="C48" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2">
         <v>20</v>
@@ -1668,244 +1668,244 @@
         <v>24</v>
       </c>
       <c r="F48" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G48" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H48" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B49" s="3">
-        <v>46061</v>
+        <v>46064</v>
       </c>
       <c r="C49" s="2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D49" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E49" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F49" s="2">
         <v>28</v>
       </c>
       <c r="G49" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H49" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B50" s="3">
-        <v>46057</v>
+        <v>46061</v>
       </c>
       <c r="C50" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E50" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F50" s="2">
         <v>28</v>
       </c>
       <c r="G50" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H50" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51" s="3">
-        <v>46054</v>
+        <v>46057</v>
       </c>
       <c r="C51" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D51" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E51" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F51" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G51" s="2">
         <v>33</v>
       </c>
       <c r="H51" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B52" s="3">
-        <v>46050</v>
+        <v>46054</v>
       </c>
       <c r="C52" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E52" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F52" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G52" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H52" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B53" s="3">
-        <v>46047</v>
+        <v>46050</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E53" s="2">
+        <v>12</v>
+      </c>
+      <c r="F53" s="2">
+        <v>13</v>
+      </c>
+      <c r="G53" s="2">
+        <v>20</v>
+      </c>
+      <c r="H53" s="2">
         <v>10</v>
-      </c>
-      <c r="F53" s="2">
-        <v>11</v>
-      </c>
-      <c r="G53" s="2">
-        <v>13</v>
-      </c>
-      <c r="H53" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B54" s="3">
-        <v>46043</v>
+        <v>46047</v>
       </c>
       <c r="C54" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D54" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E54" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F54" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G54" s="2">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H54" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B55" s="3">
-        <v>46040</v>
+        <v>46043</v>
       </c>
       <c r="C55" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D55" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E55" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F55" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G55" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H55" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B56" s="3">
-        <v>46036</v>
+        <v>46040</v>
       </c>
       <c r="C56" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F56" s="2">
+        <v>26</v>
+      </c>
+      <c r="G56" s="2">
         <v>29</v>
       </c>
-      <c r="G56" s="2">
-        <v>34</v>
-      </c>
       <c r="H56" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B57" s="3">
-        <v>46033</v>
+        <v>46036</v>
       </c>
       <c r="C57" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D57" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F57" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G57" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H57" s="2">
         <v>11</v>
@@ -1913,53 +1913,79 @@
     </row>
     <row r="58" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B58" s="3">
-        <v>46029</v>
+        <v>46033</v>
       </c>
       <c r="C58" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D58" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E58" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F58" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G58" s="2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H58" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B59" s="3">
-        <v>46026</v>
+        <v>46029</v>
       </c>
       <c r="C59" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E59" s="2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F59" s="2">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G59" s="2">
         <v>34</v>
       </c>
       <c r="H59" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
+        <v>1</v>
+      </c>
+      <c r="B60" s="3">
+        <v>46026</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <v>12</v>
+      </c>
+      <c r="E60" s="2">
+        <v>22</v>
+      </c>
+      <c r="F60" s="2">
+        <v>33</v>
+      </c>
+      <c r="G60" s="2">
+        <v>34</v>
+      </c>
+      <c r="H60" s="2">
         <v>5</v>
       </c>
     </row>

--- a/şns_topu.xlsx
+++ b/şns_topu.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\slck\Kaptan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660A6D5E-2FE7-4AA2-996D-20ECDF404FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81F6445-E78C-4C3E-83BA-0CE04E32FEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Hafta</t>
   </si>
@@ -50,12 +45,21 @@
   <si>
     <t>Artı</t>
   </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>29.07.2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,57 +67,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF114FE4"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9B363"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -121,107 +84,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF00AAE9"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF00AAE9"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF00AAE9"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF00AAE9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -244,44 +119,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -308,15 +183,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -343,7 +217,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -355,3828 +228,3864 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>59</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B3" s="1">
         <v>46229</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C3">
         <v>13</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D3">
         <v>15</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E3">
         <v>17</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F3">
         <v>18</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G3">
         <v>20</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H3">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>58</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B4" s="1">
         <v>46225</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4">
         <v>15</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4">
         <v>22</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4">
         <v>29</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G4">
         <v>30</v>
       </c>
-      <c r="H3" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="H4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>57</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B5" s="1">
         <v>46222</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5">
         <v>10</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5">
         <v>15</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5">
         <v>16</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5">
         <v>31</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G5">
         <v>34</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H5">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>56</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B6" s="1">
         <v>46218</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E6">
         <v>6</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G6">
         <v>15</v>
       </c>
-      <c r="H5" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="H6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>55</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B7" s="1">
         <v>46215</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C7">
         <v>10</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D7">
         <v>19</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E7">
         <v>22</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F7">
         <v>25</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G7">
         <v>26</v>
       </c>
-      <c r="H6" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="H7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>54</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B8" s="1">
         <v>46211</v>
       </c>
-      <c r="C7" s="1">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
         <v>14</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E8">
         <v>15</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F8">
         <v>19</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G8">
         <v>22</v>
       </c>
-      <c r="H7" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="H8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>53</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B9" s="1">
         <v>46208</v>
       </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
         <v>7</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E9">
         <v>24</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F9">
         <v>30</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G9">
         <v>32</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H9">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>52</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B10" s="1">
         <v>46204</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D10">
         <v>7</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E10">
         <v>18</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F10">
         <v>20</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G10">
         <v>34</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H10">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>51</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B11" s="1">
         <v>46201</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11">
         <v>7</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11">
         <v>13</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11">
         <v>14</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11">
         <v>29</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>50</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B12" s="1">
         <v>46197</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C12">
         <v>7</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D12">
         <v>26</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E12">
         <v>30</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F12">
         <v>32</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12">
         <v>33</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H12">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>49</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B13" s="1">
         <v>46194</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D13">
         <v>4</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E13">
         <v>19</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F13">
         <v>22</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13">
         <v>30</v>
       </c>
-      <c r="H12" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="H13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>48</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B14" s="1">
         <v>46190</v>
       </c>
-      <c r="C13" s="1">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
         <v>11</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E14">
         <v>14</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14">
         <v>22</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G14">
         <v>29</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H14">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>47</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B15" s="1">
         <v>46187</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C15">
         <v>4</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D15">
         <v>17</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E15">
         <v>21</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F15">
         <v>22</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15">
         <v>32</v>
       </c>
-      <c r="H14" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
+      <c r="H15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>46</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B16" s="1">
         <v>46183</v>
       </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
         <v>4</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E16">
         <v>13</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F16">
         <v>24</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G16">
         <v>33</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H16">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>45</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B17" s="1">
         <v>46180</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C17">
         <v>12</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D17">
         <v>15</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E17">
         <v>18</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F17">
         <v>21</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G17">
         <v>34</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H17">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>44</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B18" s="1">
         <v>46176</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C18">
         <v>7</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18">
         <v>13</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E18">
         <v>19</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F18">
         <v>21</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G18">
         <v>25</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H18">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>43</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B19" s="1">
         <v>46173</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C19">
         <v>7</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D19">
         <v>9</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E19">
         <v>10</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F19">
         <v>22</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G19">
         <v>28</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H19">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>42</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B20" s="1">
         <v>46169</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C20">
         <v>18</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20">
         <v>19</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E20">
         <v>20</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F20">
         <v>22</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G20">
         <v>27</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H20">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>41</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B21" s="1">
         <v>46156</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C21">
         <v>18</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21">
         <v>20</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E21">
         <v>26</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F21">
         <v>27</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G21">
         <v>34</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H21">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>40</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B22" s="1">
         <v>46162</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C22">
         <v>17</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D22">
         <v>18</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E22">
         <v>27</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F22">
         <v>31</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G22">
         <v>34</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H22">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>39</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B23" s="1">
         <v>46159</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C23">
         <v>11</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D23">
         <v>20</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E23">
         <v>27</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F23">
         <v>31</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G23">
         <v>32</v>
       </c>
-      <c r="H22" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
+      <c r="H23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>38</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B24" s="1">
         <v>46155</v>
       </c>
-      <c r="C23" s="1">
-        <v>5</v>
-      </c>
-      <c r="D23" s="1">
+      <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24">
         <v>7</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E24">
         <v>11</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F24">
         <v>15</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G24">
         <v>21</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H24">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>37</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B25" s="1">
         <v>46152</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C25">
         <v>4</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D25">
         <v>6</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E25">
         <v>20</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F25">
         <v>23</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G25">
         <v>33</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H25">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>36</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B26" s="1">
         <v>46148</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C26">
         <v>3</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D26">
         <v>20</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E26">
         <v>25</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F26">
         <v>32</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G26">
         <v>34</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H26">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>35</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B27" s="1">
         <v>46145</v>
       </c>
-      <c r="C26" s="1">
-        <v>2</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
         <v>9</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E27">
         <v>19</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F27">
         <v>26</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G27">
         <v>29</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H27">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>34</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B28" s="1">
         <v>46141</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C28">
         <v>1</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D28">
         <v>6</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E28">
         <v>21</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F28">
         <v>25</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G28">
         <v>34</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H28">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>33</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B29" s="1">
         <v>46138</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C29">
         <v>6</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D29">
         <v>17</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E29">
         <v>26</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F29">
         <v>29</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G29">
         <v>32</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H29">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>32</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B30" s="1">
         <v>46134</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C30">
         <v>1</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D30">
         <v>16</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E30">
         <v>24</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F30">
         <v>31</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G30">
         <v>34</v>
       </c>
-      <c r="H29" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+      <c r="H30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>31</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B31" s="1">
         <v>46131</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C31">
         <v>3</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D31">
         <v>14</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E31">
         <v>16</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F31">
         <v>17</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G31">
         <v>34</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H31">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B32" s="1">
         <v>46127</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C32">
         <v>1</v>
       </c>
-      <c r="D31" s="1">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
         <v>13</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F32">
         <v>16</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G32">
         <v>19</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H32">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>29</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B33" s="1">
         <v>46124</v>
       </c>
-      <c r="C32" s="1">
-        <v>2</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
         <v>6</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E33">
         <v>11</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F33">
         <v>19</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G33">
         <v>24</v>
       </c>
-      <c r="H32" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
+      <c r="H33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>28</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B34" s="1">
         <v>46120</v>
       </c>
-      <c r="C33" s="1">
-        <v>5</v>
-      </c>
-      <c r="D33" s="1">
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34">
         <v>17</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E34">
         <v>28</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F34">
         <v>29</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G34">
         <v>30</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H34">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>27</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B35" s="1">
         <v>46117</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C35">
         <v>9</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D35">
         <v>14</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E35">
         <v>19</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F35">
         <v>20</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G35">
         <v>25</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H35">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>26</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B36" s="1">
         <v>46113</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C36">
         <v>7</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D36">
         <v>10</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E36">
         <v>12</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F36">
         <v>13</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G36">
         <v>22</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H36">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>25</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B37" s="1">
         <v>46110</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C37">
         <v>3</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D37">
         <v>11</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E37">
         <v>12</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F37">
         <v>17</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G37">
         <v>20</v>
       </c>
-      <c r="H36" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
+      <c r="H37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>24</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B38" s="1">
         <v>46106</v>
       </c>
-      <c r="C37" s="1">
-        <v>8</v>
-      </c>
-      <c r="D37" s="1">
+      <c r="C38">
+        <v>8</v>
+      </c>
+      <c r="D38">
         <v>18</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E38">
         <v>27</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F38">
         <v>28</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G38">
         <v>31</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H38">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>23</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B39" s="1">
         <v>46103</v>
       </c>
-      <c r="C38" s="1">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1">
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
         <v>9</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E39">
         <v>15</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F39">
         <v>18</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G39">
         <v>29</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H39">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>22</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B40" s="1">
         <v>46099</v>
       </c>
-      <c r="C39" s="1">
-        <v>8</v>
-      </c>
-      <c r="D39" s="1">
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40">
         <v>13</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E40">
         <v>26</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F40">
         <v>29</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G40">
         <v>31</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H40">
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>21</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B41" s="1">
         <v>46096</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C41">
         <v>7</v>
       </c>
-      <c r="D40" s="1">
-        <v>8</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D41">
+        <v>8</v>
+      </c>
+      <c r="E41">
         <v>10</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F41">
         <v>20</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G41">
         <v>33</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H41">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>20</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B42" s="1">
         <v>46092</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C42">
         <v>6</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D42">
         <v>11</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E42">
         <v>14</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F42">
         <v>24</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G42">
         <v>27</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H42">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43">
         <v>19</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B43" s="1">
         <v>46089</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C43">
         <v>1</v>
       </c>
-      <c r="D42" s="1">
-        <v>8</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43">
         <v>23</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F43">
         <v>30</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G43">
         <v>33</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H43">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>18</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B44" s="1">
         <v>46085</v>
       </c>
-      <c r="C43" s="1">
-        <v>2</v>
-      </c>
-      <c r="D43" s="1">
-        <v>5</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44">
         <v>16</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F44">
         <v>24</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G44">
         <v>26</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H44">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>17</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B45" s="1">
         <v>46082</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C45">
         <v>1</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D45">
         <v>9</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E45">
         <v>14</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F45">
         <v>25</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G45">
         <v>31</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H45">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>16</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B46" s="1">
         <v>46078</v>
       </c>
-      <c r="C45" s="1">
-        <v>8</v>
-      </c>
-      <c r="D45" s="1">
+      <c r="C46">
+        <v>8</v>
+      </c>
+      <c r="D46">
         <v>15</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E46">
         <v>24</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F46">
         <v>26</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G46">
         <v>27</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H46">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>15</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B47" s="1">
         <v>46075</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C47">
         <v>3</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D47">
         <v>11</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E47">
         <v>24</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F47">
         <v>29</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G47">
         <v>31</v>
       </c>
-      <c r="H46" s="1">
+      <c r="H47">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>14</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B48" s="1">
         <v>46071</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C48">
         <v>6</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D48">
         <v>15</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E48">
         <v>19</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F48">
         <v>21</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G48">
         <v>23</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H48">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>13</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B49" s="1">
         <v>46068</v>
       </c>
-      <c r="C48" s="1">
-        <v>8</v>
-      </c>
-      <c r="D48" s="1">
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49">
         <v>20</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E49">
         <v>24</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F49">
         <v>30</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G49">
         <v>33</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H49">
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50">
         <v>12</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B50" s="1">
         <v>46064</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C50">
         <v>19</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D50">
         <v>20</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E50">
         <v>24</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F50">
         <v>28</v>
       </c>
-      <c r="G49" s="1">
+      <c r="G50">
         <v>32</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H50">
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>11</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B51" s="1">
         <v>46061</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C51">
         <v>4</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D51">
         <v>12</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E51">
         <v>16</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F51">
         <v>28</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G51">
         <v>29</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H51">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52">
         <v>10</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B52" s="1">
         <v>46057</v>
       </c>
-      <c r="C51" s="1">
-        <v>2</v>
-      </c>
-      <c r="D51" s="1">
-        <v>5</v>
-      </c>
-      <c r="E51" s="1">
-        <v>8</v>
-      </c>
-      <c r="F51" s="1">
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <v>8</v>
+      </c>
+      <c r="F52">
         <v>28</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G52">
         <v>33</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H52">
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>9</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B53" s="1">
         <v>46054</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C53">
         <v>9</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D53">
         <v>15</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E53">
         <v>19</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F53">
         <v>20</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G53">
         <v>33</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H53">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
-        <v>8</v>
-      </c>
-      <c r="B53" s="2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>8</v>
+      </c>
+      <c r="B54" s="1">
         <v>46050</v>
       </c>
-      <c r="C53" s="1">
-        <v>2</v>
-      </c>
-      <c r="D53" s="1">
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
         <v>4</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E54">
         <v>12</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F54">
         <v>13</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G54">
         <v>20</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H54">
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55">
         <v>7</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B55" s="1">
         <v>46047</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C55">
         <v>1</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D55">
         <v>7</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E55">
         <v>10</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F55">
         <v>11</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G55">
         <v>13</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H55">
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56">
         <v>6</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B56" s="1">
         <v>46043</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C56">
         <v>15</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D56">
         <v>16</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E56">
         <v>18</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F56">
         <v>30</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G56">
         <v>33</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H56">
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
-        <v>5</v>
-      </c>
-      <c r="B56" s="2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>5</v>
+      </c>
+      <c r="B57" s="1">
         <v>46040</v>
       </c>
-      <c r="C56" s="1">
-        <v>8</v>
-      </c>
-      <c r="D56" s="1">
+      <c r="C57">
+        <v>8</v>
+      </c>
+      <c r="D57">
         <v>9</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E57">
         <v>22</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F57">
         <v>26</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G57">
         <v>29</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H57">
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58">
         <v>4</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B58" s="1">
         <v>46036</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C58">
         <v>4</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D58">
         <v>10</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E58">
         <v>11</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F58">
         <v>29</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G58">
         <v>34</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H58">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59">
         <v>3</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B59" s="1">
         <v>46033</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C59">
         <v>7</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D59">
         <v>9</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E59">
         <v>16</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F59">
         <v>21</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G59">
         <v>26</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H59">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
-        <v>2</v>
-      </c>
-      <c r="B59" s="2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>2</v>
+      </c>
+      <c r="B60" s="1">
         <v>46029</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C60">
         <v>3</v>
       </c>
-      <c r="D59" s="1">
-        <v>5</v>
-      </c>
-      <c r="E59" s="1">
-        <v>8</v>
-      </c>
-      <c r="F59" s="1">
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+      <c r="F60">
         <v>18</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G60">
         <v>34</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H60">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61">
         <v>1</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B61" s="1">
         <v>46026</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C61">
         <v>1</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D61">
         <v>12</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E61">
         <v>22</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F61">
         <v>33</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G61">
         <v>34</v>
       </c>
-      <c r="H60" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C61" s="6">
-        <v>2</v>
-      </c>
-      <c r="D61" s="6">
-        <v>5</v>
-      </c>
-      <c r="E61" s="6">
+      <c r="H61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="E62">
         <v>11</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F62">
         <v>31</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G62">
         <v>33</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H62">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C62" s="6">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C63">
         <v>3</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D63">
         <v>12</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E63">
         <v>14</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F63">
         <v>15</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G63">
         <v>33</v>
       </c>
-      <c r="H62" s="1">
+      <c r="H63">
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C63" s="6">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C64">
         <v>1</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D64">
         <v>3</v>
       </c>
-      <c r="E63" s="6">
-        <v>8</v>
-      </c>
-      <c r="F63" s="6">
+      <c r="E64">
+        <v>8</v>
+      </c>
+      <c r="F64">
         <v>10</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G64">
         <v>34</v>
       </c>
-      <c r="H63" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C64" s="6">
+      <c r="H64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C65">
         <v>3</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D65">
         <v>6</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E65">
         <v>9</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F65">
         <v>22</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G65">
         <v>30</v>
       </c>
-      <c r="H64" s="1">
+      <c r="H65">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C65" s="6">
+    <row r="66" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C66">
         <v>4</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D66">
         <v>12</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E66">
         <v>18</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F66">
         <v>25</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G66">
         <v>29</v>
       </c>
-      <c r="H65" s="1">
+      <c r="H66">
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C66" s="6">
+    <row r="67" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C67">
         <v>9</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D67">
         <v>11</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E67">
         <v>15</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F67">
         <v>18</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G67">
         <v>33</v>
       </c>
-      <c r="H66" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C67" s="6">
-        <v>8</v>
-      </c>
-      <c r="D67" s="6">
+      <c r="H67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68">
         <v>17</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E68">
         <v>20</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F68">
         <v>30</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G68">
         <v>34</v>
       </c>
-      <c r="H67" s="1">
+      <c r="H68">
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C68" s="6">
-        <v>8</v>
-      </c>
-      <c r="D68" s="6">
+    <row r="69" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C69">
+        <v>8</v>
+      </c>
+      <c r="D69">
         <v>21</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E69">
         <v>22</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F69">
         <v>26</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G69">
         <v>29</v>
       </c>
-      <c r="H68" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C69" s="6">
-        <v>2</v>
-      </c>
-      <c r="D69" s="6">
+      <c r="H69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="D70">
         <v>6</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E70">
         <v>19</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F70">
         <v>20</v>
       </c>
-      <c r="G69" s="6">
+      <c r="G70">
         <v>22</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H70">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C70" s="6">
-        <v>5</v>
-      </c>
-      <c r="D70" s="6">
+    <row r="71" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C71">
+        <v>5</v>
+      </c>
+      <c r="D71">
         <v>15</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E71">
         <v>22</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F71">
         <v>25</v>
       </c>
-      <c r="G70" s="6">
+      <c r="G71">
         <v>27</v>
       </c>
-      <c r="H70" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C71" s="6">
-        <v>5</v>
-      </c>
-      <c r="D71" s="6">
+      <c r="H71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C72">
+        <v>5</v>
+      </c>
+      <c r="D72">
         <v>7</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E72">
         <v>21</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F72">
         <v>25</v>
       </c>
-      <c r="G71" s="6">
+      <c r="G72">
         <v>32</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H72">
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="6">
-        <v>2</v>
-      </c>
-      <c r="D72" s="6">
-        <v>8</v>
-      </c>
-      <c r="E72" s="6">
+    <row r="73" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73">
+        <v>8</v>
+      </c>
+      <c r="E73">
         <v>20</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F73">
         <v>21</v>
       </c>
-      <c r="G72" s="6">
+      <c r="G73">
         <v>27</v>
       </c>
-      <c r="H72" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C73" s="6">
+      <c r="H73">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C74">
         <v>1</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D74">
         <v>6</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E74">
         <v>10</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F74">
         <v>19</v>
       </c>
-      <c r="G73" s="6">
+      <c r="G74">
         <v>29</v>
       </c>
-      <c r="H73" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C74" s="6">
+      <c r="H74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C75">
         <v>1</v>
       </c>
-      <c r="D74" s="6">
-        <v>2</v>
-      </c>
-      <c r="E74" s="6">
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
         <v>7</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F75">
         <v>14</v>
       </c>
-      <c r="G74" s="6">
+      <c r="G75">
         <v>20</v>
       </c>
-      <c r="H74" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C75" s="6">
+      <c r="H75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C76">
         <v>3</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D76">
         <v>10</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E76">
         <v>20</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F76">
         <v>27</v>
       </c>
-      <c r="G75" s="6">
+      <c r="G76">
         <v>33</v>
       </c>
-      <c r="H75" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="6">
-        <v>2</v>
-      </c>
-      <c r="D76" s="6">
+      <c r="H76">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
         <v>24</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E77">
         <v>28</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F77">
         <v>30</v>
       </c>
-      <c r="G76" s="6">
+      <c r="G77">
         <v>33</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H77">
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="6">
+    <row r="78" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C78">
         <v>1</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D78">
         <v>7</v>
       </c>
-      <c r="E77" s="6">
-        <v>8</v>
-      </c>
-      <c r="F77" s="6">
+      <c r="E78">
+        <v>8</v>
+      </c>
+      <c r="F78">
         <v>11</v>
       </c>
-      <c r="G77" s="6">
+      <c r="G78">
         <v>22</v>
       </c>
-      <c r="H77" s="1">
+      <c r="H78">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C78" s="6">
-        <v>2</v>
-      </c>
-      <c r="D78" s="6">
-        <v>8</v>
-      </c>
-      <c r="E78" s="6">
+    <row r="79" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>8</v>
+      </c>
+      <c r="E79">
         <v>22</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F79">
         <v>25</v>
       </c>
-      <c r="G78" s="6">
+      <c r="G79">
         <v>29</v>
       </c>
-      <c r="H78" s="1">
+      <c r="H79">
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C79" s="6">
-        <v>5</v>
-      </c>
-      <c r="D79" s="6">
+    <row r="80" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C80">
+        <v>5</v>
+      </c>
+      <c r="D80">
         <v>9</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E80">
         <v>22</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F80">
         <v>23</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G80">
         <v>25</v>
       </c>
-      <c r="H79" s="1">
+      <c r="H80">
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C80" s="6">
+    <row r="81" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C81">
         <v>3</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D81">
         <v>17</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E81">
         <v>19</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F81">
         <v>26</v>
       </c>
-      <c r="G80" s="6">
+      <c r="G81">
         <v>29</v>
       </c>
-      <c r="H80" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C81" s="6">
+      <c r="H81">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C82">
         <v>7</v>
       </c>
-      <c r="D81" s="6">
+      <c r="D82">
         <v>14</v>
       </c>
-      <c r="E81" s="6">
+      <c r="E82">
         <v>15</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F82">
         <v>18</v>
       </c>
-      <c r="G81" s="6">
+      <c r="G82">
         <v>23</v>
       </c>
-      <c r="H81" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C82" s="6">
+      <c r="H82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C83">
         <v>4</v>
       </c>
-      <c r="D82" s="6">
+      <c r="D83">
         <v>6</v>
       </c>
-      <c r="E82" s="6">
+      <c r="E83">
         <v>7</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F83">
         <v>14</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G83">
         <v>29</v>
       </c>
-      <c r="H82" s="1">
+      <c r="H83">
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C83" s="6">
+    <row r="84" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C84">
         <v>4</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D84">
         <v>6</v>
       </c>
-      <c r="E83" s="6">
+      <c r="E84">
         <v>12</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F84">
         <v>18</v>
       </c>
-      <c r="G83" s="6">
+      <c r="G84">
         <v>25</v>
       </c>
-      <c r="H83" s="1">
+      <c r="H84">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C84" s="6">
+    <row r="85" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C85">
         <v>3</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D85">
         <v>12</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E85">
         <v>13</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F85">
         <v>14</v>
       </c>
-      <c r="G84" s="6">
+      <c r="G85">
         <v>17</v>
       </c>
-      <c r="H84" s="1">
+      <c r="H85">
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C85" s="6">
+    <row r="86" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C86">
         <v>4</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D86">
         <v>6</v>
       </c>
-      <c r="E85" s="6">
+      <c r="E86">
         <v>7</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F86">
         <v>16</v>
       </c>
-      <c r="G85" s="6">
+      <c r="G86">
         <v>33</v>
       </c>
-      <c r="H85" s="1">
+      <c r="H86">
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C86" s="6">
+    <row r="87" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C87">
         <v>4</v>
       </c>
-      <c r="D86" s="6">
-        <v>5</v>
-      </c>
-      <c r="E86" s="6">
+      <c r="D87">
+        <v>5</v>
+      </c>
+      <c r="E87">
         <v>11</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F87">
         <v>12</v>
       </c>
-      <c r="G86" s="6">
+      <c r="G87">
         <v>18</v>
       </c>
-      <c r="H86" s="1">
+      <c r="H87">
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C87" s="6">
+    <row r="88" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C88">
         <v>3</v>
       </c>
-      <c r="D87" s="6">
-        <v>5</v>
-      </c>
-      <c r="E87" s="6">
+      <c r="D88">
+        <v>5</v>
+      </c>
+      <c r="E88">
         <v>21</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F88">
         <v>23</v>
       </c>
-      <c r="G87" s="6">
+      <c r="G88">
         <v>26</v>
       </c>
-      <c r="H87" s="1">
+      <c r="H88">
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C88" s="6">
+    <row r="89" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C89">
         <v>6</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D89">
         <v>10</v>
       </c>
-      <c r="E88" s="6">
+      <c r="E89">
         <v>16</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F89">
         <v>21</v>
       </c>
-      <c r="G88" s="6">
+      <c r="G89">
         <v>34</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H89">
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C89" s="6">
-        <v>2</v>
-      </c>
-      <c r="D89" s="6">
-        <v>5</v>
-      </c>
-      <c r="E89" s="6">
+    <row r="90" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90">
+        <v>5</v>
+      </c>
+      <c r="E90">
         <v>12</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F90">
         <v>22</v>
       </c>
-      <c r="G89" s="6">
+      <c r="G90">
         <v>31</v>
       </c>
-      <c r="H89" s="1">
+      <c r="H90">
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C90" s="6">
+    <row r="91" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C91">
         <v>4</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D91">
         <v>6</v>
       </c>
-      <c r="E90" s="6">
-        <v>8</v>
-      </c>
-      <c r="F90" s="6">
+      <c r="E91">
+        <v>8</v>
+      </c>
+      <c r="F91">
         <v>10</v>
       </c>
-      <c r="G90" s="6">
+      <c r="G91">
         <v>31</v>
       </c>
-      <c r="H90" s="1">
+      <c r="H91">
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C91" s="6">
+    <row r="92" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C92">
         <v>16</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D92">
         <v>19</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E92">
         <v>24</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F92">
         <v>30</v>
       </c>
-      <c r="G91" s="6">
+      <c r="G92">
         <v>31</v>
       </c>
-      <c r="H91" s="1">
+      <c r="H92">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C92" s="6">
+    <row r="93" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C93">
         <v>3</v>
       </c>
-      <c r="D92" s="6">
-        <v>5</v>
-      </c>
-      <c r="E92" s="6">
+      <c r="D93">
+        <v>5</v>
+      </c>
+      <c r="E93">
         <v>25</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F93">
         <v>28</v>
       </c>
-      <c r="G92" s="6">
+      <c r="G93">
         <v>31</v>
       </c>
-      <c r="H92" s="1">
+      <c r="H93">
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C93" s="6">
+    <row r="94" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C94">
         <v>7</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D94">
         <v>19</v>
       </c>
-      <c r="E93" s="6">
+      <c r="E94">
         <v>23</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F94">
         <v>27</v>
       </c>
-      <c r="G93" s="6">
+      <c r="G94">
         <v>33</v>
       </c>
-      <c r="H93" s="1">
+      <c r="H94">
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="6">
-        <v>2</v>
-      </c>
-      <c r="D94" s="6">
-        <v>8</v>
-      </c>
-      <c r="E94" s="6">
+    <row r="95" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95">
+        <v>8</v>
+      </c>
+      <c r="E95">
         <v>17</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F95">
         <v>21</v>
       </c>
-      <c r="G94" s="6">
+      <c r="G95">
         <v>31</v>
       </c>
-      <c r="H94" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C95" s="6">
+      <c r="H95">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C96">
         <v>3</v>
       </c>
-      <c r="D95" s="6">
+      <c r="D96">
         <v>19</v>
       </c>
-      <c r="E95" s="6">
+      <c r="E96">
         <v>21</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F96">
         <v>25</v>
       </c>
-      <c r="G95" s="6">
+      <c r="G96">
         <v>34</v>
       </c>
-      <c r="H95" s="1">
+      <c r="H96">
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C96" s="6">
-        <v>8</v>
-      </c>
-      <c r="D96" s="6">
+    <row r="97" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C97">
+        <v>8</v>
+      </c>
+      <c r="D97">
         <v>28</v>
       </c>
-      <c r="E96" s="6">
+      <c r="E97">
         <v>30</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F97">
         <v>32</v>
       </c>
-      <c r="G96" s="6">
+      <c r="G97">
         <v>34</v>
       </c>
-      <c r="H96" s="1">
+      <c r="H97">
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C97" s="6">
+    <row r="98" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C98">
         <v>16</v>
       </c>
-      <c r="D97" s="6">
+      <c r="D98">
         <v>18</v>
       </c>
-      <c r="E97" s="6">
+      <c r="E98">
         <v>20</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F98">
         <v>21</v>
       </c>
-      <c r="G97" s="6">
+      <c r="G98">
         <v>32</v>
       </c>
-      <c r="H97" s="1">
+      <c r="H98">
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="6">
-        <v>8</v>
-      </c>
-      <c r="D98" s="6">
+    <row r="99" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C99">
+        <v>8</v>
+      </c>
+      <c r="D99">
         <v>10</v>
       </c>
-      <c r="E98" s="6">
+      <c r="E99">
         <v>13</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F99">
         <v>19</v>
       </c>
-      <c r="G98" s="6">
+      <c r="G99">
         <v>22</v>
       </c>
-      <c r="H98" s="1">
+      <c r="H99">
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="6">
-        <v>5</v>
-      </c>
-      <c r="D99" s="6">
+    <row r="100" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C100">
+        <v>5</v>
+      </c>
+      <c r="D100">
         <v>22</v>
       </c>
-      <c r="E99" s="6">
+      <c r="E100">
         <v>23</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F100">
         <v>28</v>
       </c>
-      <c r="G99" s="6">
+      <c r="G100">
         <v>31</v>
       </c>
-      <c r="H99" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C100" s="6">
-        <v>5</v>
-      </c>
-      <c r="D100" s="6">
+      <c r="H100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C101">
+        <v>5</v>
+      </c>
+      <c r="D101">
         <v>12</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E101">
         <v>24</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F101">
         <v>32</v>
       </c>
-      <c r="G100" s="6">
+      <c r="G101">
         <v>34</v>
       </c>
-      <c r="H100" s="1">
+      <c r="H101">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C101" s="6">
-        <v>2</v>
-      </c>
-      <c r="D101" s="6">
-        <v>8</v>
-      </c>
-      <c r="E101" s="6">
+    <row r="102" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102">
+        <v>8</v>
+      </c>
+      <c r="E102">
         <v>9</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F102">
         <v>15</v>
       </c>
-      <c r="G101" s="6">
+      <c r="G102">
         <v>19</v>
       </c>
-      <c r="H101" s="1">
+      <c r="H102">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C102" s="6">
-        <v>2</v>
-      </c>
-      <c r="D102" s="6">
+    <row r="103" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103">
         <v>16</v>
       </c>
-      <c r="E102" s="6">
+      <c r="E103">
         <v>20</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F103">
         <v>29</v>
       </c>
-      <c r="G102" s="6">
+      <c r="G103">
         <v>34</v>
       </c>
-      <c r="H102" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C103" s="6">
+      <c r="H103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C104">
         <v>15</v>
       </c>
-      <c r="D103" s="6">
+      <c r="D104">
         <v>17</v>
       </c>
-      <c r="E103" s="6">
+      <c r="E104">
         <v>22</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F104">
         <v>24</v>
       </c>
-      <c r="G103" s="6">
+      <c r="G104">
         <v>29</v>
       </c>
-      <c r="H103" s="1">
+      <c r="H104">
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C104" s="6">
+    <row r="105" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C105">
         <v>4</v>
       </c>
-      <c r="D104" s="6">
+      <c r="D105">
         <v>14</v>
       </c>
-      <c r="E104" s="6">
+      <c r="E105">
         <v>15</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F105">
         <v>17</v>
       </c>
-      <c r="G104" s="6">
+      <c r="G105">
         <v>28</v>
       </c>
-      <c r="H104" s="1">
+      <c r="H105">
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C105" s="6">
-        <v>2</v>
-      </c>
-      <c r="D105" s="6">
+    <row r="106" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C106">
+        <v>2</v>
+      </c>
+      <c r="D106">
         <v>3</v>
       </c>
-      <c r="E105" s="6">
+      <c r="E106">
         <v>10</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F106">
         <v>16</v>
       </c>
-      <c r="G105" s="6">
+      <c r="G106">
         <v>23</v>
       </c>
-      <c r="H105" s="1">
+      <c r="H106">
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C106" s="6">
+    <row r="107" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C107">
         <v>4</v>
       </c>
-      <c r="D106" s="6">
+      <c r="D107">
         <v>7</v>
       </c>
-      <c r="E106" s="6">
+      <c r="E107">
         <v>10</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F107">
         <v>11</v>
       </c>
-      <c r="G106" s="6">
+      <c r="G107">
         <v>27</v>
       </c>
-      <c r="H106" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C107" s="6">
+      <c r="H107">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C108">
         <v>1</v>
       </c>
-      <c r="D107" s="6">
-        <v>5</v>
-      </c>
-      <c r="E107" s="6">
+      <c r="D108">
+        <v>5</v>
+      </c>
+      <c r="E108">
         <v>20</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F108">
         <v>23</v>
       </c>
-      <c r="G107" s="6">
+      <c r="G108">
         <v>29</v>
       </c>
-      <c r="H107" s="1">
+      <c r="H108">
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C108" s="6">
+    <row r="109" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C109">
         <v>1</v>
       </c>
-      <c r="D108" s="6">
-        <v>8</v>
-      </c>
-      <c r="E108" s="6">
+      <c r="D109">
+        <v>8</v>
+      </c>
+      <c r="E109">
         <v>16</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F109">
         <v>17</v>
       </c>
-      <c r="G108" s="6">
+      <c r="G109">
         <v>22</v>
       </c>
-      <c r="H108" s="1">
+      <c r="H109">
         <v>14</v>
       </c>
     </row>
-    <row r="109" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C109" s="6">
-        <v>5</v>
-      </c>
-      <c r="D109" s="6">
-        <v>8</v>
-      </c>
-      <c r="E109" s="6">
+    <row r="110" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C110">
+        <v>5</v>
+      </c>
+      <c r="D110">
+        <v>8</v>
+      </c>
+      <c r="E110">
         <v>14</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F110">
         <v>15</v>
       </c>
-      <c r="G109" s="6">
+      <c r="G110">
         <v>33</v>
       </c>
-      <c r="H109" s="1">
+      <c r="H110">
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C110" s="6">
-        <v>2</v>
-      </c>
-      <c r="D110" s="6">
+    <row r="111" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111">
         <v>20</v>
       </c>
-      <c r="E110" s="6">
+      <c r="E111">
         <v>25</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F111">
         <v>27</v>
       </c>
-      <c r="G110" s="6">
+      <c r="G111">
         <v>33</v>
       </c>
-      <c r="H110" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C111" s="6">
-        <v>5</v>
-      </c>
-      <c r="D111" s="6">
+      <c r="H111">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C112">
+        <v>5</v>
+      </c>
+      <c r="D112">
         <v>7</v>
       </c>
-      <c r="E111" s="6">
+      <c r="E112">
         <v>12</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F112">
         <v>21</v>
       </c>
-      <c r="G111" s="6">
+      <c r="G112">
         <v>31</v>
       </c>
-      <c r="H111" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C112" s="6">
+      <c r="H112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C113">
         <v>1</v>
       </c>
-      <c r="D112" s="6">
-        <v>2</v>
-      </c>
-      <c r="E112" s="6">
+      <c r="D113">
+        <v>2</v>
+      </c>
+      <c r="E113">
         <v>4</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F113">
         <v>7</v>
       </c>
-      <c r="G112" s="6">
+      <c r="G113">
         <v>16</v>
       </c>
-      <c r="H112" s="1">
+      <c r="H113">
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C113" s="6">
+    <row r="114" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C114">
         <v>7</v>
       </c>
-      <c r="D113" s="6">
+      <c r="D114">
         <v>15</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E114">
         <v>16</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F114">
         <v>26</v>
       </c>
-      <c r="G113" s="6">
+      <c r="G114">
         <v>30</v>
       </c>
-      <c r="H113" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C114" s="6">
+      <c r="H114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C115">
         <v>9</v>
       </c>
-      <c r="D114" s="6">
+      <c r="D115">
         <v>18</v>
       </c>
-      <c r="E114" s="6">
+      <c r="E115">
         <v>22</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F115">
         <v>32</v>
       </c>
-      <c r="G114" s="6">
+      <c r="G115">
         <v>33</v>
       </c>
-      <c r="H114" s="1">
+      <c r="H115">
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C115" s="6">
-        <v>8</v>
-      </c>
-      <c r="D115" s="6">
+    <row r="116" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C116">
+        <v>8</v>
+      </c>
+      <c r="D116">
         <v>10</v>
       </c>
-      <c r="E115" s="6">
+      <c r="E116">
         <v>12</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F116">
         <v>20</v>
       </c>
-      <c r="G115" s="6">
+      <c r="G116">
         <v>28</v>
       </c>
-      <c r="H115" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="6">
-        <v>5</v>
-      </c>
-      <c r="D116" s="6">
+      <c r="H116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C117">
+        <v>5</v>
+      </c>
+      <c r="D117">
         <v>6</v>
       </c>
-      <c r="E116" s="6">
+      <c r="E117">
         <v>21</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F117">
         <v>22</v>
       </c>
-      <c r="G116" s="6">
+      <c r="G117">
         <v>31</v>
       </c>
-      <c r="H116" s="1">
+      <c r="H117">
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C117" s="6">
+    <row r="118" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C118">
         <v>13</v>
       </c>
-      <c r="D117" s="6">
+      <c r="D118">
         <v>17</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E118">
         <v>30</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F118">
         <v>32</v>
       </c>
-      <c r="G117" s="6">
+      <c r="G118">
         <v>34</v>
       </c>
-      <c r="H117" s="1">
+      <c r="H118">
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C118" s="6">
+    <row r="119" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C119">
         <v>14</v>
       </c>
-      <c r="D118" s="6">
+      <c r="D119">
         <v>18</v>
       </c>
-      <c r="E118" s="6">
+      <c r="E119">
         <v>19</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F119">
         <v>20</v>
       </c>
-      <c r="G118" s="6">
+      <c r="G119">
         <v>27</v>
       </c>
-      <c r="H118" s="1">
+      <c r="H119">
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C119" s="6">
+    <row r="120" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C120">
         <v>1</v>
       </c>
-      <c r="D119" s="6">
+      <c r="D120">
         <v>9</v>
       </c>
-      <c r="E119" s="6">
+      <c r="E120">
         <v>18</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F120">
         <v>22</v>
       </c>
-      <c r="G119" s="6">
+      <c r="G120">
         <v>25</v>
       </c>
-      <c r="H119" s="1">
+      <c r="H120">
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C120" s="6">
+    <row r="121" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C121">
         <v>3</v>
       </c>
-      <c r="D120" s="6">
+      <c r="D121">
         <v>7</v>
       </c>
-      <c r="E120" s="6">
-        <v>8</v>
-      </c>
-      <c r="F120" s="6">
+      <c r="E121">
+        <v>8</v>
+      </c>
+      <c r="F121">
         <v>16</v>
       </c>
-      <c r="G120" s="6">
+      <c r="G121">
         <v>21</v>
       </c>
-      <c r="H120" s="1">
+      <c r="H121">
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C121" s="6">
-        <v>5</v>
-      </c>
-      <c r="D121" s="6">
+    <row r="122" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C122">
+        <v>5</v>
+      </c>
+      <c r="D122">
         <v>11</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E122">
         <v>23</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F122">
         <v>27</v>
       </c>
-      <c r="G121" s="6">
+      <c r="G122">
         <v>30</v>
       </c>
-      <c r="H121" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C122" s="6">
+      <c r="H122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C123">
         <v>12</v>
       </c>
-      <c r="D122" s="6">
+      <c r="D123">
         <v>13</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E123">
         <v>18</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F123">
         <v>21</v>
       </c>
-      <c r="G122" s="6">
+      <c r="G123">
         <v>26</v>
       </c>
-      <c r="H122" s="1">
+      <c r="H123">
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C123" s="6">
+    <row r="124" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C124">
         <v>6</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D124">
         <v>7</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E124">
         <v>9</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F124">
         <v>15</v>
       </c>
-      <c r="G123" s="6">
+      <c r="G124">
         <v>26</v>
       </c>
-      <c r="H123" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C124" s="6">
+      <c r="H124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C125">
         <v>1</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D125">
         <v>12</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E125">
         <v>22</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F125">
         <v>25</v>
       </c>
-      <c r="G124" s="6">
+      <c r="G125">
         <v>28</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H125">
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C125" s="6">
+    <row r="126" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C126">
         <v>1</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D126">
         <v>4</v>
       </c>
-      <c r="E125" s="6">
+      <c r="E126">
         <v>11</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F126">
         <v>13</v>
       </c>
-      <c r="G125" s="6">
+      <c r="G126">
         <v>29</v>
       </c>
-      <c r="H125" s="1">
+      <c r="H126">
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C126" s="6">
+    <row r="127" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C127">
         <v>1</v>
       </c>
-      <c r="D126" s="6">
-        <v>5</v>
-      </c>
-      <c r="E126" s="6">
+      <c r="D127">
+        <v>5</v>
+      </c>
+      <c r="E127">
         <v>9</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F127">
         <v>22</v>
       </c>
-      <c r="G126" s="6">
+      <c r="G127">
         <v>24</v>
       </c>
-      <c r="H126" s="1">
+      <c r="H127">
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C127" s="6">
+    <row r="128" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C128">
         <v>10</v>
       </c>
-      <c r="D127" s="6">
+      <c r="D128">
         <v>13</v>
       </c>
-      <c r="E127" s="6">
+      <c r="E128">
         <v>16</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F128">
         <v>22</v>
       </c>
-      <c r="G127" s="6">
+      <c r="G128">
         <v>29</v>
       </c>
-      <c r="H127" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C128" s="6">
+      <c r="H128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C129">
         <v>3</v>
       </c>
-      <c r="D128" s="6">
+      <c r="D129">
         <v>12</v>
       </c>
-      <c r="E128" s="6">
+      <c r="E129">
         <v>13</v>
       </c>
-      <c r="F128" s="6">
+      <c r="F129">
         <v>22</v>
       </c>
-      <c r="G128" s="6">
+      <c r="G129">
         <v>23</v>
       </c>
-      <c r="H128" s="1">
+      <c r="H129">
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C129" s="6">
+    <row r="130" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C130">
         <v>4</v>
       </c>
-      <c r="D129" s="6">
-        <v>8</v>
-      </c>
-      <c r="E129" s="6">
+      <c r="D130">
+        <v>8</v>
+      </c>
+      <c r="E130">
         <v>17</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F130">
         <v>22</v>
       </c>
-      <c r="G129" s="6">
+      <c r="G130">
         <v>28</v>
       </c>
-      <c r="H129" s="1">
+      <c r="H130">
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C130" s="6">
-        <v>2</v>
-      </c>
-      <c r="D130" s="6">
+    <row r="131" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C131">
+        <v>2</v>
+      </c>
+      <c r="D131">
         <v>21</v>
       </c>
-      <c r="E130" s="6">
+      <c r="E131">
         <v>24</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F131">
         <v>30</v>
       </c>
-      <c r="G130" s="6">
+      <c r="G131">
         <v>33</v>
       </c>
-      <c r="H130" s="1">
+      <c r="H131">
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C131" s="6">
+    <row r="132" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C132">
         <v>22</v>
       </c>
-      <c r="D131" s="6">
+      <c r="D132">
         <v>25</v>
       </c>
-      <c r="E131" s="6">
+      <c r="E132">
         <v>31</v>
       </c>
-      <c r="F131" s="6">
+      <c r="F132">
         <v>32</v>
       </c>
-      <c r="G131" s="6">
+      <c r="G132">
         <v>33</v>
       </c>
-      <c r="H131" s="1">
+      <c r="H132">
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C132" s="6">
-        <v>8</v>
-      </c>
-      <c r="D132" s="6">
+    <row r="133" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C133">
+        <v>8</v>
+      </c>
+      <c r="D133">
         <v>10</v>
       </c>
-      <c r="E132" s="6">
+      <c r="E133">
         <v>11</v>
       </c>
-      <c r="F132" s="6">
+      <c r="F133">
         <v>28</v>
       </c>
-      <c r="G132" s="6">
+      <c r="G133">
         <v>32</v>
       </c>
-      <c r="H132" s="1">
+      <c r="H133">
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C133" s="6">
-        <v>5</v>
-      </c>
-      <c r="D133" s="6">
+    <row r="134" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C134">
+        <v>5</v>
+      </c>
+      <c r="D134">
         <v>17</v>
       </c>
-      <c r="E133" s="6">
+      <c r="E134">
         <v>19</v>
       </c>
-      <c r="F133" s="6">
+      <c r="F134">
         <v>23</v>
       </c>
-      <c r="G133" s="6">
+      <c r="G134">
         <v>29</v>
       </c>
-      <c r="H133" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C134" s="6">
+      <c r="H134">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C135">
         <v>1</v>
       </c>
-      <c r="D134" s="6">
+      <c r="D135">
         <v>15</v>
       </c>
-      <c r="E134" s="6">
+      <c r="E135">
         <v>22</v>
       </c>
-      <c r="F134" s="6">
+      <c r="F135">
         <v>23</v>
       </c>
-      <c r="G134" s="6">
+      <c r="G135">
         <v>32</v>
       </c>
-      <c r="H134" s="1">
+      <c r="H135">
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C135" s="6">
+    <row r="136" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C136">
         <v>14</v>
       </c>
-      <c r="D135" s="6">
+      <c r="D136">
         <v>15</v>
       </c>
-      <c r="E135" s="6">
+      <c r="E136">
         <v>19</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F136">
         <v>20</v>
       </c>
-      <c r="G135" s="6">
+      <c r="G136">
         <v>32</v>
       </c>
-      <c r="H135" s="1">
+      <c r="H136">
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C136" s="6">
+    <row r="137" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C137">
         <v>7</v>
       </c>
-      <c r="D136" s="6">
+      <c r="D137">
         <v>9</v>
       </c>
-      <c r="E136" s="6">
+      <c r="E137">
         <v>14</v>
       </c>
-      <c r="F136" s="6">
+      <c r="F137">
         <v>26</v>
       </c>
-      <c r="G136" s="6">
+      <c r="G137">
         <v>32</v>
       </c>
-      <c r="H136" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C137" s="6">
-        <v>2</v>
-      </c>
-      <c r="D137" s="6">
+      <c r="H137">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C138">
+        <v>2</v>
+      </c>
+      <c r="D138">
         <v>6</v>
       </c>
-      <c r="E137" s="6">
+      <c r="E138">
         <v>18</v>
       </c>
-      <c r="F137" s="6">
+      <c r="F138">
         <v>26</v>
       </c>
-      <c r="G137" s="6">
+      <c r="G138">
         <v>33</v>
       </c>
-      <c r="H137" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C138" s="6">
+      <c r="H138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C139">
         <v>7</v>
       </c>
-      <c r="D138" s="6">
-        <v>8</v>
-      </c>
-      <c r="E138" s="6">
+      <c r="D139">
+        <v>8</v>
+      </c>
+      <c r="E139">
         <v>22</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F139">
         <v>25</v>
       </c>
-      <c r="G138" s="6">
+      <c r="G139">
         <v>32</v>
       </c>
-      <c r="H138" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="139" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C139" s="6">
-        <v>2</v>
-      </c>
-      <c r="D139" s="6">
+      <c r="H139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C140">
+        <v>2</v>
+      </c>
+      <c r="D140">
         <v>15</v>
       </c>
-      <c r="E139" s="6">
+      <c r="E140">
         <v>25</v>
       </c>
-      <c r="F139" s="6">
+      <c r="F140">
         <v>28</v>
       </c>
-      <c r="G139" s="6">
+      <c r="G140">
         <v>32</v>
       </c>
-      <c r="H139" s="1">
+      <c r="H140">
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C140" s="6">
-        <v>5</v>
-      </c>
-      <c r="D140" s="6">
+    <row r="141" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C141">
+        <v>5</v>
+      </c>
+      <c r="D141">
         <v>6</v>
       </c>
-      <c r="E140" s="6">
-        <v>8</v>
-      </c>
-      <c r="F140" s="6">
+      <c r="E141">
+        <v>8</v>
+      </c>
+      <c r="F141">
         <v>22</v>
       </c>
-      <c r="G140" s="6">
+      <c r="G141">
         <v>32</v>
       </c>
-      <c r="H140" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C141" s="6">
-        <v>5</v>
-      </c>
-      <c r="D141" s="6">
+      <c r="H141">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C142">
+        <v>5</v>
+      </c>
+      <c r="D142">
         <v>9</v>
       </c>
-      <c r="E141" s="6">
+      <c r="E142">
         <v>10</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F142">
         <v>13</v>
       </c>
-      <c r="G141" s="6">
+      <c r="G142">
         <v>14</v>
       </c>
-      <c r="H141" s="1">
+      <c r="H142">
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C142" s="6">
+    <row r="143" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C143">
         <v>3</v>
       </c>
-      <c r="D142" s="6">
+      <c r="D143">
         <v>26</v>
       </c>
-      <c r="E142" s="6">
+      <c r="E143">
         <v>27</v>
       </c>
-      <c r="F142" s="6">
+      <c r="F143">
         <v>29</v>
       </c>
-      <c r="G142" s="6">
+      <c r="G143">
         <v>33</v>
       </c>
-      <c r="H142" s="1">
+      <c r="H143">
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C143" s="6">
-        <v>2</v>
-      </c>
-      <c r="D143" s="6">
-        <v>5</v>
-      </c>
-      <c r="E143" s="6">
+    <row r="144" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144">
+        <v>5</v>
+      </c>
+      <c r="E144">
         <v>12</v>
       </c>
-      <c r="F143" s="6">
+      <c r="F144">
         <v>19</v>
       </c>
-      <c r="G143" s="6">
+      <c r="G144">
         <v>27</v>
       </c>
-      <c r="H143" s="1">
+      <c r="H144">
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C144" s="6">
+    <row r="145" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C145">
         <v>1</v>
       </c>
-      <c r="D144" s="6">
+      <c r="D145">
         <v>13</v>
       </c>
-      <c r="E144" s="6">
+      <c r="E145">
         <v>15</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F145">
         <v>25</v>
       </c>
-      <c r="G144" s="6">
+      <c r="G145">
         <v>34</v>
       </c>
-      <c r="H144" s="1">
+      <c r="H145">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C145" s="6">
+    <row r="146" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C146">
         <v>3</v>
       </c>
-      <c r="D145" s="6">
-        <v>5</v>
-      </c>
-      <c r="E145" s="6">
+      <c r="D146">
+        <v>5</v>
+      </c>
+      <c r="E146">
         <v>18</v>
       </c>
-      <c r="F145" s="6">
+      <c r="F146">
         <v>23</v>
       </c>
-      <c r="G145" s="6">
+      <c r="G146">
         <v>27</v>
       </c>
-      <c r="H145" s="1">
+      <c r="H146">
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C146" s="6">
+    <row r="147" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C147">
         <v>3</v>
       </c>
-      <c r="D146" s="6">
+      <c r="D147">
         <v>19</v>
       </c>
-      <c r="E146" s="6">
+      <c r="E147">
         <v>21</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F147">
         <v>32</v>
       </c>
-      <c r="G146" s="6">
+      <c r="G147">
         <v>33</v>
       </c>
-      <c r="H146" s="1">
+      <c r="H147">
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C147" s="6">
+    <row r="148" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C148">
         <v>4</v>
       </c>
-      <c r="D147" s="6">
+      <c r="D148">
         <v>15</v>
       </c>
-      <c r="E147" s="6">
+      <c r="E148">
         <v>19</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F148">
         <v>24</v>
       </c>
-      <c r="G147" s="6">
+      <c r="G148">
         <v>27</v>
       </c>
-      <c r="H147" s="1">
+      <c r="H148">
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C148" s="6">
+    <row r="149" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C149">
         <v>3</v>
       </c>
-      <c r="D148" s="6">
+      <c r="D149">
         <v>20</v>
       </c>
-      <c r="E148" s="6">
+      <c r="E149">
         <v>21</v>
       </c>
-      <c r="F148" s="6">
+      <c r="F149">
         <v>25</v>
       </c>
-      <c r="G148" s="6">
+      <c r="G149">
         <v>34</v>
       </c>
-      <c r="H148" s="1">
+      <c r="H149">
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C149" s="6">
+    <row r="150" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C150">
         <v>11</v>
       </c>
-      <c r="D149" s="6">
+      <c r="D150">
         <v>20</v>
       </c>
-      <c r="E149" s="6">
+      <c r="E150">
         <v>24</v>
       </c>
-      <c r="F149" s="6">
+      <c r="F150">
         <v>26</v>
       </c>
-      <c r="G149" s="6">
+      <c r="G150">
         <v>29</v>
       </c>
-      <c r="H149" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="150" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C150" s="6">
+      <c r="H150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C151">
         <v>4</v>
       </c>
-      <c r="D150" s="6">
+      <c r="D151">
         <v>22</v>
       </c>
-      <c r="E150" s="6">
+      <c r="E151">
         <v>26</v>
       </c>
-      <c r="F150" s="6">
+      <c r="F151">
         <v>31</v>
       </c>
-      <c r="G150" s="6">
+      <c r="G151">
         <v>32</v>
       </c>
-      <c r="H150" s="1">
+      <c r="H151">
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C151" s="6">
-        <v>2</v>
-      </c>
-      <c r="D151" s="6">
-        <v>5</v>
-      </c>
-      <c r="E151" s="6">
+    <row r="152" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C152">
+        <v>2</v>
+      </c>
+      <c r="D152">
+        <v>5</v>
+      </c>
+      <c r="E152">
         <v>9</v>
       </c>
-      <c r="F151" s="6">
+      <c r="F152">
         <v>17</v>
       </c>
-      <c r="G151" s="6">
+      <c r="G152">
         <v>25</v>
       </c>
-      <c r="H151" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="152" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C152" s="6">
-        <v>2</v>
-      </c>
-      <c r="D152" s="6">
+      <c r="H152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C153">
+        <v>2</v>
+      </c>
+      <c r="D153">
         <v>10</v>
       </c>
-      <c r="E152" s="6">
+      <c r="E153">
         <v>15</v>
       </c>
-      <c r="F152" s="6">
+      <c r="F153">
         <v>17</v>
       </c>
-      <c r="G152" s="6">
+      <c r="G153">
         <v>23</v>
       </c>
-      <c r="H152" s="1">
+      <c r="H153">
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C153" s="6">
+    <row r="154" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C154">
         <v>10</v>
       </c>
-      <c r="D153" s="6">
+      <c r="D154">
         <v>13</v>
       </c>
-      <c r="E153" s="6">
+      <c r="E154">
         <v>19</v>
       </c>
-      <c r="F153" s="6">
+      <c r="F154">
         <v>27</v>
       </c>
-      <c r="G153" s="6">
+      <c r="G154">
         <v>31</v>
       </c>
-      <c r="H153" s="1">
+      <c r="H154">
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C154" s="6">
+    <row r="155" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C155">
         <v>1</v>
       </c>
-      <c r="D154" s="6">
-        <v>8</v>
-      </c>
-      <c r="E154" s="6">
+      <c r="D155">
+        <v>8</v>
+      </c>
+      <c r="E155">
         <v>18</v>
       </c>
-      <c r="F154" s="6">
+      <c r="F155">
         <v>27</v>
       </c>
-      <c r="G154" s="6">
+      <c r="G155">
         <v>29</v>
       </c>
-      <c r="H154" s="1">
+      <c r="H155">
         <v>10</v>
       </c>
     </row>
-    <row r="155" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C155" s="6">
-        <v>2</v>
-      </c>
-      <c r="D155" s="6">
+    <row r="156" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C156">
+        <v>2</v>
+      </c>
+      <c r="D156">
         <v>4</v>
       </c>
-      <c r="E155" s="6">
-        <v>8</v>
-      </c>
-      <c r="F155" s="6">
+      <c r="E156">
+        <v>8</v>
+      </c>
+      <c r="F156">
         <v>9</v>
       </c>
-      <c r="G155" s="6">
+      <c r="G156">
         <v>20</v>
       </c>
-      <c r="H155" s="1">
+      <c r="H156">
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C156" s="6">
+    <row r="157" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C157">
         <v>6</v>
       </c>
-      <c r="D156" s="6">
+      <c r="D157">
         <v>17</v>
       </c>
-      <c r="E156" s="6">
+      <c r="E157">
         <v>18</v>
       </c>
-      <c r="F156" s="6">
+      <c r="F157">
         <v>23</v>
       </c>
-      <c r="G156" s="6">
+      <c r="G157">
         <v>28</v>
       </c>
-      <c r="H156" s="1">
+      <c r="H157">
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C157" s="6">
-        <v>2</v>
-      </c>
-      <c r="D157" s="6">
+    <row r="158" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C158">
+        <v>2</v>
+      </c>
+      <c r="D158">
         <v>10</v>
       </c>
-      <c r="E157" s="6">
+      <c r="E158">
         <v>15</v>
       </c>
-      <c r="F157" s="6">
+      <c r="F158">
         <v>16</v>
       </c>
-      <c r="G157" s="6">
+      <c r="G158">
         <v>30</v>
       </c>
-      <c r="H157" s="1">
+      <c r="H158">
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C158" s="6">
-        <v>5</v>
-      </c>
-      <c r="D158" s="6">
+    <row r="159" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C159">
+        <v>5</v>
+      </c>
+      <c r="D159">
         <v>9</v>
       </c>
-      <c r="E158" s="6">
+      <c r="E159">
         <v>18</v>
       </c>
-      <c r="F158" s="6">
+      <c r="F159">
         <v>22</v>
       </c>
-      <c r="G158" s="6">
+      <c r="G159">
         <v>31</v>
       </c>
-      <c r="H158" s="1">
+      <c r="H159">
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C159" s="6">
+    <row r="160" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C160">
         <v>6</v>
       </c>
-      <c r="D159" s="6">
+      <c r="D160">
         <v>9</v>
       </c>
-      <c r="E159" s="6">
+      <c r="E160">
         <v>19</v>
       </c>
-      <c r="F159" s="6">
+      <c r="F160">
         <v>25</v>
       </c>
-      <c r="G159" s="6">
+      <c r="G160">
         <v>30</v>
       </c>
-      <c r="H159" s="1">
+      <c r="H160">
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C160" s="6">
+    <row r="161" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C161">
         <v>9</v>
       </c>
-      <c r="D160" s="6">
+      <c r="D161">
         <v>14</v>
       </c>
-      <c r="E160" s="6">
+      <c r="E161">
         <v>29</v>
       </c>
-      <c r="F160" s="6">
+      <c r="F161">
         <v>31</v>
       </c>
-      <c r="G160" s="6">
+      <c r="G161">
         <v>33</v>
       </c>
-      <c r="H160" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="161" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C161" s="6">
-        <v>2</v>
-      </c>
-      <c r="D161" s="6">
-        <v>8</v>
-      </c>
-      <c r="E161" s="6">
+      <c r="H161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C162">
+        <v>2</v>
+      </c>
+      <c r="D162">
+        <v>8</v>
+      </c>
+      <c r="E162">
         <v>22</v>
       </c>
-      <c r="F161" s="6">
+      <c r="F162">
         <v>31</v>
       </c>
-      <c r="G161" s="6">
+      <c r="G162">
         <v>32</v>
       </c>
-      <c r="H161" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="162" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C162" s="6">
+      <c r="H162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C163">
         <v>6</v>
       </c>
-      <c r="D162" s="6">
+      <c r="D163">
         <v>16</v>
       </c>
-      <c r="E162" s="6">
+      <c r="E163">
         <v>32</v>
       </c>
-      <c r="F162" s="6">
+      <c r="F163">
         <v>33</v>
       </c>
-      <c r="G162" s="6">
+      <c r="G163">
         <v>34</v>
       </c>
-      <c r="H162" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="163" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C163" s="6">
+      <c r="H163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C164">
         <v>21</v>
       </c>
-      <c r="D163" s="6">
+      <c r="D164">
         <v>23</v>
       </c>
-      <c r="E163" s="6">
+      <c r="E164">
         <v>24</v>
       </c>
-      <c r="F163" s="6">
+      <c r="F164">
         <v>26</v>
       </c>
-      <c r="G163" s="6">
+      <c r="G164">
         <v>34</v>
       </c>
-      <c r="H163" s="1">
+      <c r="H164">
         <v>14</v>
       </c>
     </row>
-    <row r="164" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C164" s="6">
-        <v>8</v>
-      </c>
-      <c r="D164" s="6">
+    <row r="165" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C165">
+        <v>8</v>
+      </c>
+      <c r="D165">
         <v>10</v>
       </c>
-      <c r="E164" s="6">
+      <c r="E165">
         <v>16</v>
       </c>
-      <c r="F164" s="6">
+      <c r="F165">
         <v>31</v>
       </c>
-      <c r="G164" s="6">
+      <c r="G165">
         <v>34</v>
       </c>
-      <c r="H164" s="1">
+      <c r="H165">
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C165" s="6">
+    <row r="166" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C166">
         <v>1</v>
       </c>
-      <c r="D165" s="6">
-        <v>5</v>
-      </c>
-      <c r="E165" s="6">
-        <v>8</v>
-      </c>
-      <c r="F165" s="6">
+      <c r="D166">
+        <v>5</v>
+      </c>
+      <c r="E166">
+        <v>8</v>
+      </c>
+      <c r="F166">
         <v>13</v>
       </c>
-      <c r="G165" s="6">
+      <c r="G166">
         <v>19</v>
       </c>
-      <c r="H165" s="1">
+      <c r="H166">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C61:G165">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>18</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>8</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
-      <formula>3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>